--- a/Test_Log.xlsx
+++ b/Test_Log.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Student\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Student\Documents\GitHub\angry-birds-clone-assignment-SundaysWithoutGod\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB4F4834-511A-4F6E-B11A-90989029A770}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7DE2719-FD49-4B44-A8D2-8CF08144710D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F675273F-C51E-4954-B235-DAD390D71047}"/>
   </bookViews>
@@ -189,7 +189,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="36">
   <si>
     <t>Date:</t>
   </si>
@@ -276,6 +276,57 @@
 will be equal to the 
 number I am testing it 
 against</t>
+  </si>
+  <si>
+    <t>I created a bird class that can be used repeatedly 
+instead of having to create individual ones for every
+test. I used the bird class to access the position of the 
+box2D body on the sprite to check if they are working
+correctly.</t>
+  </si>
+  <si>
+    <t>The X position on the box2D 
+body is equal to a value I set</t>
+  </si>
+  <si>
+    <t>The two positions will be
+equal</t>
+  </si>
+  <si>
+    <t>Test Failed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The box2D body needs to be checked, 
+because the test failed and when I checked 
+what value the box2D body is 0.777778 but 
+the set position is 23.3333 </t>
+  </si>
+  <si>
+    <t>The sprite position will be
+greater than 0</t>
+  </si>
+  <si>
+    <t>The sprite position will be
+greater than 0 because the
+sprite is being genreated</t>
+  </si>
+  <si>
+    <t>Using the bird class I got the X position of the bird 
+sprite to see if was greater than 0 to make sure the
+sprite is working correctly.</t>
+  </si>
+  <si>
+    <t>Checking the sprite is being
+loaded</t>
+  </si>
+  <si>
+    <t>Using the bird class to access the get sprite funtion to 
+check if the sprite is being loaded using the expect true
+test.</t>
+  </si>
+  <si>
+    <t>The test will return true 
+and pass</t>
   </si>
 </sst>
 </file>
@@ -525,7 +576,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
@@ -563,6 +614,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -926,7 +980,9 @@
       <c r="A2" s="14">
         <v>1</v>
       </c>
-      <c r="B2" s="15"/>
+      <c r="B2" s="15">
+        <v>46134</v>
+      </c>
       <c r="C2" s="16"/>
       <c r="D2" s="24" t="s">
         <v>11</v>
@@ -950,7 +1006,9 @@
         <f>A2+1</f>
         <v>2</v>
       </c>
-      <c r="B3" s="3"/>
+      <c r="B3" s="3">
+        <v>46134</v>
+      </c>
       <c r="C3" s="9"/>
       <c r="D3" s="27" t="s">
         <v>13</v>
@@ -1017,46 +1075,78 @@
       </c>
       <c r="I5" s="12"/>
     </row>
-    <row r="6" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="75.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B6" s="3"/>
+      <c r="B6" s="3">
+        <v>46162</v>
+      </c>
       <c r="C6" s="9"/>
-      <c r="D6" s="6"/>
+      <c r="D6" s="27" t="s">
+        <v>25</v>
+      </c>
       <c r="E6" s="9"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="12"/>
-    </row>
-    <row r="7" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="F6" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="G6" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="I6" s="29" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B7" s="3"/>
+      <c r="B7" s="3">
+        <v>46162</v>
+      </c>
       <c r="C7" s="9"/>
-      <c r="D7" s="6"/>
+      <c r="D7" s="27" t="s">
+        <v>32</v>
+      </c>
       <c r="E7" s="9"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="6"/>
+      <c r="F7" s="27" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="I7" s="12"/>
     </row>
-    <row r="8" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B8" s="3"/>
+      <c r="B8" s="3">
+        <v>46165</v>
+      </c>
       <c r="C8" s="9"/>
-      <c r="D8" s="6"/>
+      <c r="D8" s="27" t="s">
+        <v>34</v>
+      </c>
       <c r="E8" s="9"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="6"/>
+      <c r="F8" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="G8" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="I8" s="12"/>
     </row>
     <row r="9" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
@@ -1066,12 +1156,12 @@
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="9"/>
-      <c r="D9" s="6"/>
+      <c r="D9" s="27"/>
       <c r="E9" s="9"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="9"/>
+      <c r="F9" s="27"/>
+      <c r="G9" s="28"/>
       <c r="H9" s="6"/>
-      <c r="I9" s="12"/>
+      <c r="I9" s="29"/>
     </row>
     <row r="10" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="1">

--- a/Test_Log.xlsx
+++ b/Test_Log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Student\Documents\GitHub\angry-birds-clone-assignment-SundaysWithoutGod\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7DE2719-FD49-4B44-A8D2-8CF08144710D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5946E03-DDFA-4BF8-B155-EFDECF3A5E9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F675273F-C51E-4954-B235-DAD390D71047}"/>
   </bookViews>
@@ -189,7 +189,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="42">
   <si>
     <t>Date:</t>
   </si>
@@ -258,9 +258,6 @@
   </si>
   <si>
     <t>The scale that I set will be the same as the scale I'm using to test</t>
-  </si>
-  <si>
-    <t>Test passed</t>
   </si>
   <si>
     <t>Testing to see if the pig health will be lowered when I use the damage function</t>
@@ -296,12 +293,6 @@
     <t>Test Failed</t>
   </si>
   <si>
-    <t xml:space="preserve">The box2D body needs to be checked, 
-because the test failed and when I checked 
-what value the box2D body is 0.777778 but 
-the set position is 23.3333 </t>
-  </si>
-  <si>
     <t>The sprite position will be
 greater than 0</t>
   </si>
@@ -320,13 +311,43 @@
 loaded</t>
   </si>
   <si>
-    <t>Using the bird class to access the get sprite funtion to 
-check if the sprite is being loaded using the expect true
-test.</t>
-  </si>
-  <si>
-    <t>The test will return true 
-and pass</t>
+    <t>cc36600</t>
+  </si>
+  <si>
+    <t>The test will return false because the sprite will load meaning the test has  passed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Testing to see if the sprite is loading by using the bird class fixture and an Expect_false statement. I created a bool load sprite funtion for the expect_false that will be false if the sprite dosen't load and true if it does. The test should fail bacause the sprite should load 
+</t>
+  </si>
+  <si>
+    <t>Creating a parameter test to see if the movement of my dynamic bird object is correct across a varitey of values using the sprite position</t>
+  </si>
+  <si>
+    <t>using the EXPECT_EQ, The values of the bird object will match the values I set for the parameters in the movement test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The ASSERT_EQ  results will pass </t>
+  </si>
+  <si>
+    <t>I changed the Box 2D test that was checking if the X 
+position was equal to a value I set to checking if the
+sprite position is equal to a value I set.</t>
+  </si>
+  <si>
+    <t>The X position on the sprite is equal to a value I set</t>
+  </si>
+  <si>
+    <t>The EXPECT_EQ will pass 
+because both values will
+be the same</t>
+  </si>
+  <si>
+    <t>The box2D body needs to be checked, 
+because the test failed and when I checked 
+what value the box2D body is 0.777778 but 
+the set position is 23.3333 
+The implematation of the test is not giving the correct results because of the way I had done my overlap for the box2D and SFML. It dosen't work outside of the main game the same way.</t>
   </si>
 </sst>
 </file>
@@ -997,7 +1018,7 @@
         <v>12</v>
       </c>
       <c r="H2" s="17" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I2" s="18"/>
     </row>
@@ -1023,7 +1044,7 @@
         <v>19</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I3" s="12"/>
     </row>
@@ -1041,7 +1062,7 @@
         <v>8</v>
       </c>
       <c r="F4" s="27" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G4" s="28" t="s">
         <v>17</v>
@@ -1059,23 +1080,23 @@
       <c r="B5" s="3"/>
       <c r="C5" s="9"/>
       <c r="D5" s="27" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="27" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G5" s="28" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I5" s="12"/>
     </row>
-    <row r="6" spans="1:9" ht="75.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="135" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -1085,20 +1106,20 @@
       </c>
       <c r="C6" s="9"/>
       <c r="D6" s="27" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E6" s="9"/>
       <c r="F6" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="G6" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="G6" s="28" t="s">
+      <c r="H6" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="H6" s="6" t="s">
-        <v>28</v>
-      </c>
       <c r="I6" s="29" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
@@ -1109,29 +1130,31 @@
       <c r="B7" s="3">
         <v>46162</v>
       </c>
-      <c r="C7" s="9"/>
+      <c r="C7" s="9" t="s">
+        <v>32</v>
+      </c>
       <c r="D7" s="27" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E7" s="9"/>
       <c r="F7" s="27" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G7" s="28" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I7" s="12"/>
     </row>
-    <row r="8" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="B8" s="3">
-        <v>46165</v>
+        <v>46168</v>
       </c>
       <c r="C8" s="9"/>
       <c r="D8" s="27" t="s">
@@ -1139,41 +1162,61 @@
       </c>
       <c r="E8" s="9"/>
       <c r="F8" s="27" t="s">
+        <v>31</v>
+      </c>
+      <c r="G8" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="G8" s="28" t="s">
+      <c r="H8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I8" s="12"/>
+    </row>
+    <row r="9" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B9" s="3">
+        <v>46168</v>
+      </c>
+      <c r="C9" s="9"/>
+      <c r="D9" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="H8" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="I8" s="12"/>
-    </row>
-    <row r="9" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="1">
-        <f t="shared" si="0"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="G9" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I9" s="29"/>
+    </row>
+    <row r="10" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B10" s="3">
+        <v>46168</v>
+      </c>
+      <c r="C10" s="9"/>
+      <c r="D10" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="E10" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="27"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="27"/>
-      <c r="G9" s="28"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="29"/>
-    </row>
-    <row r="10" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="1">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="9"/>
+      <c r="F10" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G10" s="28" t="s">
+        <v>40</v>
+      </c>
       <c r="H10" s="6"/>
       <c r="I10" s="12"/>
     </row>

--- a/Test_Log.xlsx
+++ b/Test_Log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Student\Documents\GitHub\angry-birds-clone-assignment-SundaysWithoutGod\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5946E03-DDFA-4BF8-B155-EFDECF3A5E9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C04097E-D1FE-4564-A365-2B0C1C519245}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F675273F-C51E-4954-B235-DAD390D71047}"/>
   </bookViews>
@@ -189,7 +189,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="52">
   <si>
     <t>Date:</t>
   </si>
@@ -235,10 +235,6 @@
   <si>
     <t xml:space="preserve">Creating a pig sprite and testing if the scalling works 
 on the SFML sprites </t>
-  </si>
-  <si>
-    <t>If the scale for the SFML 
-for the sprite works</t>
   </si>
   <si>
     <t>If the position for the SFML 
@@ -330,11 +326,6 @@
     <t xml:space="preserve">The ASSERT_EQ  results will pass </t>
   </si>
   <si>
-    <t>I changed the Box 2D test that was checking if the X 
-position was equal to a value I set to checking if the
-sprite position is equal to a value I set.</t>
-  </si>
-  <si>
     <t>The X position on the sprite is equal to a value I set</t>
   </si>
   <si>
@@ -348,6 +339,52 @@
 what value the box2D body is 0.777778 but 
 the set position is 23.3333 
 The implematation of the test is not giving the correct results because of the way I had done my overlap for the box2D and SFML. It dosen't work outside of the main game the same way.</t>
+  </si>
+  <si>
+    <t>37b0e8d</t>
+  </si>
+  <si>
+    <t>fdcfb05</t>
+  </si>
+  <si>
+    <t>1db563e</t>
+  </si>
+  <si>
+    <t>EXPECT_EQ test to check if the postiion of the sprite is equal to a value I set</t>
+  </si>
+  <si>
+    <t>Test will pass</t>
+  </si>
+  <si>
+    <t>c4263d6</t>
+  </si>
+  <si>
+    <t>b53a660</t>
+  </si>
+  <si>
+    <t>If the scale for the SFML 
+for the sprite works by testing if the EXPECT_EQ comes back as passed</t>
+  </si>
+  <si>
+    <t>I changed the Box 2D test that was checking if the X 
+position was equal to a value I set to checking if the
+sprite position is equal to a value I set as a fixed Test.</t>
+  </si>
+  <si>
+    <t>It won't allow the values to be changed or 
+register the new set position value. Changed from a shared pointer that resets to what's in the constructor regardless if I use the set position functions. To a unique pointer that deletes the pointer after the test is finished 
+everything in set up is called new.</t>
+  </si>
+  <si>
+    <t>Creating a fixture test for UI to check if the placement 
+of the UI is corrext in relation to the size of the window 
+screen. I made the UI smaller in the window screen and 
+checked the values were less than the window using 
+EXPECT_LE</t>
+  </si>
+  <si>
+    <t>The UI text will be less than 
+the window screen</t>
   </si>
 </sst>
 </file>
@@ -954,7 +991,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56B8A181-42A1-40D2-86A6-EC17E1D54CA5}">
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.109375" bestFit="1" customWidth="1"/>
@@ -1004,7 +1041,9 @@
       <c r="B2" s="15">
         <v>46134</v>
       </c>
-      <c r="C2" s="16"/>
+      <c r="C2" s="16" t="s">
+        <v>40</v>
+      </c>
       <c r="D2" s="24" t="s">
         <v>11</v>
       </c>
@@ -1012,75 +1051,80 @@
         <v>8</v>
       </c>
       <c r="F2" s="26" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G2" s="25" t="s">
         <v>12</v>
       </c>
       <c r="H2" s="17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I2" s="18"/>
     </row>
-    <row r="3" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A3" s="1">
+    <row r="3" spans="1:9" ht="77.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="14"/>
+      <c r="B3" s="15">
+        <v>46134</v>
+      </c>
+      <c r="C3" s="16"/>
+      <c r="D3" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" s="18"/>
+    </row>
+    <row r="4" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
         <f>A2+1</f>
         <v>2</v>
       </c>
-      <c r="B3" s="3">
-        <v>46134</v>
-      </c>
-      <c r="C3" s="9"/>
-      <c r="D3" s="27" t="s">
+      <c r="B4" s="3">
+        <v>46141</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D4" s="27" t="s">
         <v>13</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" s="28" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I3" s="12"/>
-    </row>
-    <row r="4" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A4" s="1">
-        <f t="shared" ref="A4:A49" si="0">A3+1</f>
-        <v>3</v>
-      </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="27" t="s">
-        <v>16</v>
       </c>
       <c r="E4" s="9" t="s">
         <v>8</v>
       </c>
       <c r="F4" s="27" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="G4" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H4" s="6" t="s">
-        <v>18</v>
-      </c>
       <c r="I4" s="12"/>
     </row>
-    <row r="5" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="9"/>
+        <f t="shared" ref="A5:A50" si="0">A4+1</f>
+        <v>3</v>
+      </c>
+      <c r="B5" s="3">
+        <v>46142</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>41</v>
+      </c>
       <c r="D5" s="27" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>8</v>
@@ -1089,169 +1133,213 @@
         <v>22</v>
       </c>
       <c r="G5" s="28" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I5" s="12"/>
     </row>
-    <row r="6" spans="1:9" ht="135" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
-        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B6" s="3">
+        <v>46141</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="G6" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I6" s="12"/>
+    </row>
+    <row r="7" spans="1:9" ht="135" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
         <v>5</v>
-      </c>
-      <c r="B6" s="3">
-        <v>46162</v>
-      </c>
-      <c r="C6" s="9"/>
-      <c r="D6" s="27" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" s="9"/>
-      <c r="F6" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="G6" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="I6" s="29" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A7" s="1">
-        <f t="shared" si="0"/>
-        <v>6</v>
       </c>
       <c r="B7" s="3">
         <v>46162</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>30</v>
-      </c>
-      <c r="E7" s="9"/>
+        <v>23</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="F7" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="G7" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="I7" s="29" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B8" s="3">
+        <v>46162</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="G7" s="28" t="s">
+      <c r="E8" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="H7" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I7" s="12"/>
-    </row>
-    <row r="8" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A8" s="1">
+      <c r="G8" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I8" s="12"/>
+    </row>
+    <row r="9" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
         <f t="shared" si="0"/>
         <v>7</v>
-      </c>
-      <c r="B8" s="3">
-        <v>46168</v>
-      </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="27" t="s">
-        <v>34</v>
-      </c>
-      <c r="E8" s="9"/>
-      <c r="F8" s="27" t="s">
-        <v>31</v>
-      </c>
-      <c r="G8" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I8" s="12"/>
-    </row>
-    <row r="9" spans="1:9" ht="72" x14ac:dyDescent="0.3">
-      <c r="A9" s="1">
-        <f t="shared" si="0"/>
-        <v>8</v>
       </c>
       <c r="B9" s="3">
         <v>46168</v>
       </c>
-      <c r="C9" s="9"/>
+      <c r="C9" s="9" t="s">
+        <v>46</v>
+      </c>
       <c r="D9" s="27" t="s">
-        <v>35</v>
-      </c>
-      <c r="E9" s="9"/>
+        <v>33</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="F9" s="27" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G9" s="28" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I9" s="29"/>
-    </row>
-    <row r="10" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+      <c r="I9" s="12"/>
+    </row>
+    <row r="10" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" s="3">
         <v>46168</v>
       </c>
-      <c r="C10" s="9"/>
+      <c r="C10" s="9" t="s">
+        <v>46</v>
+      </c>
       <c r="D10" s="27" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E10" s="9" t="s">
         <v>8</v>
       </c>
       <c r="F10" s="27" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G10" s="28" t="s">
-        <v>40</v>
-      </c>
-      <c r="H10" s="6"/>
-      <c r="I10" s="12"/>
-    </row>
-    <row r="11" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I10" s="29"/>
+    </row>
+    <row r="11" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B11" s="3">
+        <v>46168</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="G11" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="I11" s="29" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="12"/>
-    </row>
-    <row r="12" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="1">
-        <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="B12" s="3"/>
+      <c r="B12" s="3">
+        <v>46169</v>
+      </c>
       <c r="C12" s="9"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="6"/>
+      <c r="D12" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>17</v>
+      </c>
       <c r="I12" s="12"/>
     </row>
     <row r="13" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="9"/>
@@ -1265,7 +1353,7 @@
     <row r="14" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="9"/>
@@ -1279,7 +1367,7 @@
     <row r="15" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="9"/>
@@ -1293,7 +1381,7 @@
     <row r="16" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B16" s="3"/>
       <c r="C16" s="9"/>
@@ -1307,7 +1395,7 @@
     <row r="17" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="9"/>
@@ -1321,7 +1409,7 @@
     <row r="18" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="9"/>
@@ -1335,7 +1423,7 @@
     <row r="19" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" s="3"/>
       <c r="C19" s="9"/>
@@ -1349,7 +1437,7 @@
     <row r="20" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="9"/>
@@ -1363,7 +1451,7 @@
     <row r="21" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="9"/>
@@ -1377,7 +1465,7 @@
     <row r="22" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B22" s="3"/>
       <c r="C22" s="9"/>
@@ -1391,7 +1479,7 @@
     <row r="23" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B23" s="3"/>
       <c r="C23" s="9"/>
@@ -1405,7 +1493,7 @@
     <row r="24" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B24" s="3"/>
       <c r="C24" s="9"/>
@@ -1419,7 +1507,7 @@
     <row r="25" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B25" s="3"/>
       <c r="C25" s="9"/>
@@ -1433,7 +1521,7 @@
     <row r="26" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B26" s="3"/>
       <c r="C26" s="9"/>
@@ -1447,7 +1535,7 @@
     <row r="27" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B27" s="3"/>
       <c r="C27" s="9"/>
@@ -1461,7 +1549,7 @@
     <row r="28" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B28" s="3"/>
       <c r="C28" s="9"/>
@@ -1475,7 +1563,7 @@
     <row r="29" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B29" s="3"/>
       <c r="C29" s="9"/>
@@ -1489,7 +1577,7 @@
     <row r="30" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B30" s="3"/>
       <c r="C30" s="9"/>
@@ -1503,7 +1591,7 @@
     <row r="31" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="9"/>
@@ -1517,7 +1605,7 @@
     <row r="32" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B32" s="3"/>
       <c r="C32" s="9"/>
@@ -1531,7 +1619,7 @@
     <row r="33" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <f t="shared" si="0"/>
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B33" s="3"/>
       <c r="C33" s="9"/>
@@ -1545,7 +1633,7 @@
     <row r="34" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <f t="shared" si="0"/>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B34" s="3"/>
       <c r="C34" s="9"/>
@@ -1559,7 +1647,7 @@
     <row r="35" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <f t="shared" si="0"/>
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B35" s="3"/>
       <c r="C35" s="9"/>
@@ -1573,7 +1661,7 @@
     <row r="36" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <f t="shared" si="0"/>
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B36" s="3"/>
       <c r="C36" s="9"/>
@@ -1587,7 +1675,7 @@
     <row r="37" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <f t="shared" si="0"/>
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B37" s="3"/>
       <c r="C37" s="9"/>
@@ -1601,7 +1689,7 @@
     <row r="38" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <f t="shared" si="0"/>
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B38" s="3"/>
       <c r="C38" s="9"/>
@@ -1615,7 +1703,7 @@
     <row r="39" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <f t="shared" si="0"/>
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B39" s="3"/>
       <c r="C39" s="9"/>
@@ -1629,7 +1717,7 @@
     <row r="40" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <f t="shared" si="0"/>
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B40" s="3"/>
       <c r="C40" s="9"/>
@@ -1643,7 +1731,7 @@
     <row r="41" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <f t="shared" si="0"/>
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B41" s="3"/>
       <c r="C41" s="9"/>
@@ -1657,7 +1745,7 @@
     <row r="42" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <f t="shared" si="0"/>
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B42" s="3"/>
       <c r="C42" s="9"/>
@@ -1671,7 +1759,7 @@
     <row r="43" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <f t="shared" si="0"/>
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B43" s="3"/>
       <c r="C43" s="9"/>
@@ -1685,7 +1773,7 @@
     <row r="44" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <f t="shared" si="0"/>
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B44" s="3"/>
       <c r="C44" s="9"/>
@@ -1699,7 +1787,7 @@
     <row r="45" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <f t="shared" si="0"/>
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B45" s="3"/>
       <c r="C45" s="9"/>
@@ -1713,7 +1801,7 @@
     <row r="46" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <f t="shared" si="0"/>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B46" s="3"/>
       <c r="C46" s="9"/>
@@ -1727,7 +1815,7 @@
     <row r="47" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <f t="shared" si="0"/>
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B47" s="3"/>
       <c r="C47" s="9"/>
@@ -1741,7 +1829,7 @@
     <row r="48" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <f t="shared" si="0"/>
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B48" s="3"/>
       <c r="C48" s="9"/>
@@ -1752,19 +1840,33 @@
       <c r="H48" s="6"/>
       <c r="I48" s="12"/>
     </row>
-    <row r="49" spans="1:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="2">
+    <row r="49" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A49" s="1">
+        <f t="shared" si="0"/>
+        <v>47</v>
+      </c>
+      <c r="B49" s="3"/>
+      <c r="C49" s="9"/>
+      <c r="D49" s="6"/>
+      <c r="E49" s="9"/>
+      <c r="F49" s="6"/>
+      <c r="G49" s="9"/>
+      <c r="H49" s="6"/>
+      <c r="I49" s="12"/>
+    </row>
+    <row r="50" spans="1:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="2">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
-      <c r="B49" s="4"/>
-      <c r="C49" s="10"/>
-      <c r="D49" s="7"/>
-      <c r="E49" s="10"/>
-      <c r="F49" s="7"/>
-      <c r="G49" s="10"/>
-      <c r="H49" s="7"/>
-      <c r="I49" s="13"/>
+      <c r="B50" s="4"/>
+      <c r="C50" s="10"/>
+      <c r="D50" s="7"/>
+      <c r="E50" s="10"/>
+      <c r="F50" s="7"/>
+      <c r="G50" s="10"/>
+      <c r="H50" s="7"/>
+      <c r="I50" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1777,7 +1879,7 @@
           <x14:formula1>
             <xm:f>Sheet2!$A$1:$A$2</xm:f>
           </x14:formula1>
-          <xm:sqref>E2:E50</xm:sqref>
+          <xm:sqref>E2:E51</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/Test_Log.xlsx
+++ b/Test_Log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Student\Documents\GitHub\angry-birds-clone-assignment-SundaysWithoutGod\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C04097E-D1FE-4564-A365-2B0C1C519245}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56BCE844-9FC9-4474-8780-BB5BBB9B5220}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F675273F-C51E-4954-B235-DAD390D71047}"/>
   </bookViews>
@@ -189,7 +189,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="54">
   <si>
     <t>Date:</t>
   </si>
@@ -385,6 +385,12 @@
   <si>
     <t>The UI text will be less than 
 the window screen</t>
+  </si>
+  <si>
+    <t>98b6503</t>
+  </si>
+  <si>
+    <t>Changed the parameters of size in the UI to be lar</t>
   </si>
 </sst>
 </file>
@@ -1318,7 +1324,9 @@
       <c r="B12" s="3">
         <v>46169</v>
       </c>
-      <c r="C12" s="9"/>
+      <c r="C12" s="9" t="s">
+        <v>52</v>
+      </c>
       <c r="D12" s="27" t="s">
         <v>50</v>
       </c>
@@ -1341,9 +1349,13 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B13" s="3"/>
+      <c r="B13" s="3">
+        <v>46169</v>
+      </c>
       <c r="C13" s="9"/>
-      <c r="D13" s="6"/>
+      <c r="D13" s="6" t="s">
+        <v>53</v>
+      </c>
       <c r="E13" s="9"/>
       <c r="F13" s="6"/>
       <c r="G13" s="9"/>

--- a/Test_Log.xlsx
+++ b/Test_Log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Student\Documents\GitHub\angry-birds-clone-assignment-SundaysWithoutGod\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56BCE844-9FC9-4474-8780-BB5BBB9B5220}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5A3586B-9F3E-49D1-A521-FE2682BCC3B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F675273F-C51E-4954-B235-DAD390D71047}"/>
   </bookViews>
@@ -189,7 +189,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="58">
   <si>
     <t>Date:</t>
   </si>
@@ -376,21 +376,37 @@
 everything in set up is called new.</t>
   </si>
   <si>
+    <t>The UI text will be less than 
+the window screen</t>
+  </si>
+  <si>
+    <t>98b6503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The test will fail because the
+UI position will be greater 
+than the window size </t>
+  </si>
+  <si>
     <t>Creating a fixture test for UI to check if the placement 
 of the UI is corrext in relation to the size of the window 
-screen. I made the UI smaller in the window screen and 
-checked the values were less than the window using 
-EXPECT_LE</t>
-  </si>
-  <si>
-    <t>The UI text will be less than 
-the window screen</t>
-  </si>
-  <si>
-    <t>98b6503</t>
-  </si>
-  <si>
-    <t>Changed the parameters of size in the UI to be lar</t>
+screen. I made the UI parameters smaller so they fit in the window screen and checked the values were less than the window using EXPECT_LE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I changed the parameters of size in the UI to be larger
+than the window size. So it will be out of frame to make sure it's working correctly. </t>
+  </si>
+  <si>
+    <t>f77e37c</t>
+  </si>
+  <si>
+    <t>The first Assert will pass and
+the second, third ones will fail</t>
+  </si>
+  <si>
+    <t>Testing the relation between one bird and three pigs by
+using Asserts. First making pigFunc ASSERT_EQ to the 
+bird which will pass since both are at the same position, pigTest and pig are equal but will fail since I set the positions differently.</t>
   </si>
 </sst>
 </file>
@@ -1316,7 +1332,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -1325,16 +1341,16 @@
         <v>46169</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D12" s="27" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E12" s="9" t="s">
         <v>8</v>
       </c>
       <c r="F12" s="27" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G12" s="9" t="s">
         <v>44</v>
@@ -1344,7 +1360,7 @@
       </c>
       <c r="I12" s="12"/>
     </row>
-    <row r="13" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -1352,28 +1368,50 @@
       <c r="B13" s="3">
         <v>46169</v>
       </c>
-      <c r="C13" s="9"/>
-      <c r="D13" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="E13" s="9"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="6"/>
+      <c r="C13" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D13" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>17</v>
+      </c>
       <c r="I13" s="12"/>
     </row>
-    <row r="14" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B14" s="3"/>
+      <c r="B14" s="3">
+        <v>46169</v>
+      </c>
       <c r="C14" s="9"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="6"/>
+      <c r="D14" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>17</v>
+      </c>
       <c r="I14" s="12"/>
     </row>
     <row r="15" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">

--- a/Test_Log.xlsx
+++ b/Test_Log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Student\Documents\GitHub\angry-birds-clone-assignment-SundaysWithoutGod\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5A3586B-9F3E-49D1-A521-FE2682BCC3B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B604B4D2-4D6F-419F-BA3C-0E3B94157010}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F675273F-C51E-4954-B235-DAD390D71047}"/>
   </bookViews>
@@ -189,7 +189,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="61">
   <si>
     <t>Date:</t>
   </si>
@@ -400,13 +400,25 @@
     <t>f77e37c</t>
   </si>
   <si>
-    <t>The first Assert will pass and
-the second, third ones will fail</t>
-  </si>
-  <si>
     <t>Testing the relation between one bird and three pigs by
 using Asserts. First making pigFunc ASSERT_EQ to the 
 bird which will pass since both are at the same position, pigTest and pig are equal but will fail since I set the positions differently.</t>
+  </si>
+  <si>
+    <t>a9eae68</t>
+  </si>
+  <si>
+    <t>The first Assert will pass and
+the second, third ones will fail
+making the whole test a fail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All three tests will pass </t>
+  </si>
+  <si>
+    <t>Testing the relation between one bird and three pigs by
+using Asserts. First making pigFunc ASSERT_EQ to the 
+bird which will pass since both are at the same position, and changing the pigTest and pig to ASSERT_GE so they're bigger than the bird pos.</t>
   </si>
 </sst>
 </file>
@@ -1398,13 +1410,13 @@
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E14" s="9" t="s">
         <v>8</v>
       </c>
       <c r="F14" s="27" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G14" s="9" t="s">
         <v>44</v>
@@ -1414,17 +1426,29 @@
       </c>
       <c r="I14" s="12"/>
     </row>
-    <row r="15" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="9"/>
+      <c r="B15" s="3">
+        <v>46169</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>44</v>
+      </c>
       <c r="H15" s="6"/>
       <c r="I15" s="12"/>
     </row>

--- a/Test_Log.xlsx
+++ b/Test_Log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Student\Documents\GitHub\angry-birds-clone-assignment-SundaysWithoutGod\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B604B4D2-4D6F-419F-BA3C-0E3B94157010}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA0FA7FC-D73A-4CBC-A1B3-2D0DDEA26593}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F675273F-C51E-4954-B235-DAD390D71047}"/>
   </bookViews>
@@ -405,9 +405,6 @@
 bird which will pass since both are at the same position, pigTest and pig are equal but will fail since I set the positions differently.</t>
   </si>
   <si>
-    <t>a9eae68</t>
-  </si>
-  <si>
     <t>The first Assert will pass and
 the second, third ones will fail
 making the whole test a fail</t>
@@ -416,9 +413,12 @@
     <t xml:space="preserve">All three tests will pass </t>
   </si>
   <si>
+    <t>669c71b</t>
+  </si>
+  <si>
     <t>Testing the relation between one bird and three pigs by
 using Asserts. First making pigFunc ASSERT_EQ to the 
-bird which will pass since both are at the same position, and changing the pigTest and pig to ASSERT_GE so they're bigger than the bird pos.</t>
+bird which will pass since both are at the same position, and changing the pigTest and pig to ASSERT_LE so they're bigger than the bird pos.</t>
   </si>
 </sst>
 </file>
@@ -1408,7 +1408,9 @@
       <c r="B14" s="3">
         <v>46169</v>
       </c>
-      <c r="C14" s="9"/>
+      <c r="C14" s="9" t="s">
+        <v>59</v>
+      </c>
       <c r="D14" s="27" t="s">
         <v>56</v>
       </c>
@@ -1416,7 +1418,7 @@
         <v>8</v>
       </c>
       <c r="F14" s="27" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G14" s="9" t="s">
         <v>44</v>
@@ -1434,9 +1436,7 @@
       <c r="B15" s="3">
         <v>46169</v>
       </c>
-      <c r="C15" s="9" t="s">
-        <v>57</v>
-      </c>
+      <c r="C15" s="9"/>
       <c r="D15" s="27" t="s">
         <v>60</v>
       </c>
@@ -1444,7 +1444,7 @@
         <v>8</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G15" s="9" t="s">
         <v>44</v>

--- a/Test_Log.xlsx
+++ b/Test_Log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Student\Documents\GitHub\angry-birds-clone-assignment-SundaysWithoutGod\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA0FA7FC-D73A-4CBC-A1B3-2D0DDEA26593}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4961974-D9C6-496A-B50B-F8792E05C49A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F675273F-C51E-4954-B235-DAD390D71047}"/>
   </bookViews>
@@ -189,7 +189,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="62">
   <si>
     <t>Date:</t>
   </si>
@@ -419,6 +419,9 @@
     <t>Testing the relation between one bird and three pigs by
 using Asserts. First making pigFunc ASSERT_EQ to the 
 bird which will pass since both are at the same position, and changing the pigTest and pig to ASSERT_LE so they're bigger than the bird pos.</t>
+  </si>
+  <si>
+    <t>f564bba</t>
   </si>
 </sst>
 </file>
@@ -1436,7 +1439,9 @@
       <c r="B15" s="3">
         <v>46169</v>
       </c>
-      <c r="C15" s="9"/>
+      <c r="C15" s="9" t="s">
+        <v>61</v>
+      </c>
       <c r="D15" s="27" t="s">
         <v>60</v>
       </c>
@@ -1449,7 +1454,9 @@
       <c r="G15" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="H15" s="6"/>
+      <c r="H15" s="6" t="s">
+        <v>17</v>
+      </c>
       <c r="I15" s="12"/>
     </row>
     <row r="16" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">

--- a/Test_Log.xlsx
+++ b/Test_Log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Student\Documents\GitHub\angry-birds-clone-assignment-SundaysWithoutGod\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4961974-D9C6-496A-B50B-F8792E05C49A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CEEA03A-3913-4D86-A98B-8B44B35CB5C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F675273F-C51E-4954-B235-DAD390D71047}"/>
   </bookViews>
@@ -189,7 +189,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="59">
   <si>
     <t>Date:</t>
   </si>
@@ -254,15 +254,6 @@
   </si>
   <si>
     <t>The scale that I set will be the same as the scale I'm using to test</t>
-  </si>
-  <si>
-    <t>Testing to see if the pig health will be lowered when I use the damage function</t>
-  </si>
-  <si>
-    <t>The health, that is set to 70 will be lower than or equal to 0 when the take damage is 80</t>
-  </si>
-  <si>
-    <t>The damage system works and will affect the health by lowering it</t>
   </si>
   <si>
     <t>If I set the health, I will be able to use the getter to retreieve it and the health 
@@ -400,11 +391,6 @@
     <t>f77e37c</t>
   </si>
   <si>
-    <t>Testing the relation between one bird and three pigs by
-using Asserts. First making pigFunc ASSERT_EQ to the 
-bird which will pass since both are at the same position, pigTest and pig are equal but will fail since I set the positions differently.</t>
-  </si>
-  <si>
     <t>The first Assert will pass and
 the second, third ones will fail
 making the whole test a fail</t>
@@ -422,6 +408,10 @@
   </si>
   <si>
     <t>f564bba</t>
+  </si>
+  <si>
+    <t>Testing the relation between one bird and three pigs by using Asserts. First making pigFunc ASSERT_EQ to the 
+bird which will pass since both are at the same position, pigTest and pig are equal but will fail since I set the positions differently. The pigTest will fail stoping the the pig from running because it's an assert</t>
   </si>
 </sst>
 </file>
@@ -1028,7 +1018,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56B8A181-42A1-40D2-86A6-EC17E1D54CA5}">
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.109375" bestFit="1" customWidth="1"/>
@@ -1079,7 +1069,7 @@
         <v>46134</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D2" s="24" t="s">
         <v>11</v>
@@ -1098,287 +1088,292 @@
       </c>
       <c r="I2" s="18"/>
     </row>
-    <row r="3" spans="1:9" ht="77.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="14"/>
-      <c r="B3" s="15">
-        <v>46134</v>
-      </c>
-      <c r="C3" s="16"/>
-      <c r="D3" s="24" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="26" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" s="25" t="s">
-        <v>20</v>
-      </c>
-      <c r="H3" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="I3" s="18"/>
-    </row>
-    <row r="4" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="1">
+    <row r="3" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
         <f>A2+1</f>
         <v>2</v>
       </c>
+      <c r="B3" s="3">
+        <v>46141</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D3" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="G3" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" s="12"/>
+    </row>
+    <row r="4" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <f t="shared" ref="A4:A49" si="0">A3+1</f>
+        <v>3</v>
+      </c>
       <c r="B4" s="3">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D4" s="27" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E4" s="9" t="s">
         <v>8</v>
       </c>
       <c r="F4" s="27" t="s">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="G4" s="28" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H4" s="6" t="s">
         <v>17</v>
       </c>
       <c r="I4" s="12"/>
     </row>
-    <row r="5" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
-        <f t="shared" ref="A5:A50" si="0">A4+1</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" s="3">
-        <v>46142</v>
+        <v>46141</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="27" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="G5" s="28" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="H5" s="6" t="s">
         <v>17</v>
       </c>
       <c r="I5" s="12"/>
     </row>
-    <row r="6" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="135" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" s="3">
-        <v>46141</v>
+        <v>46162</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="D6" s="27" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E6" s="9" t="s">
         <v>8</v>
       </c>
       <c r="F6" s="27" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="G6" s="28" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="I6" s="12"/>
-    </row>
-    <row r="7" spans="1:9" ht="135" customHeight="1" x14ac:dyDescent="0.3">
+        <v>23</v>
+      </c>
+      <c r="I6" s="29" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>6</v>
       </c>
       <c r="B7" s="3">
         <v>46162</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>8</v>
       </c>
       <c r="F7" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="G7" s="28" t="s">
-        <v>25</v>
-      </c>
       <c r="H7" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="I7" s="29" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+      <c r="I7" s="12"/>
+    </row>
+    <row r="8" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" s="3">
-        <v>46162</v>
+        <v>46168</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="D8" s="27" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E8" s="9" t="s">
         <v>8</v>
       </c>
       <c r="F8" s="27" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G8" s="28" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H8" s="6" t="s">
         <v>17</v>
       </c>
       <c r="I8" s="12"/>
     </row>
-    <row r="9" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9" s="3">
         <v>46168</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>8</v>
       </c>
       <c r="F9" s="27" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G9" s="28" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="I9" s="12"/>
-    </row>
-    <row r="10" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+      <c r="I9" s="29"/>
+    </row>
+    <row r="10" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" s="3">
         <v>46168</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D10" s="27" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="E10" s="9" t="s">
         <v>8</v>
       </c>
       <c r="F10" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="G10" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="G10" s="28" t="s">
-        <v>36</v>
-      </c>
       <c r="H10" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="I10" s="29"/>
-    </row>
-    <row r="11" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
+        <v>23</v>
+      </c>
+      <c r="I10" s="29" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11" s="3">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>8</v>
       </c>
       <c r="F11" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="G11" s="28" t="s">
-        <v>38</v>
+        <v>47</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>41</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="I11" s="29" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+      <c r="I11" s="12"/>
+    </row>
+    <row r="12" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B12" s="3">
         <v>46169</v>
       </c>
       <c r="C12" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D12" s="27" t="s">
         <v>51</v>
-      </c>
-      <c r="D12" s="27" t="s">
-        <v>53</v>
       </c>
       <c r="E12" s="9" t="s">
         <v>8</v>
       </c>
       <c r="F12" s="27" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>17</v>
       </c>
       <c r="I12" s="12"/>
     </row>
-    <row r="13" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13" s="3">
         <v>46169</v>
@@ -1387,32 +1382,32 @@
         <v>55</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>8</v>
       </c>
       <c r="F13" s="27" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>17</v>
       </c>
       <c r="I13" s="12"/>
     </row>
-    <row r="14" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="120" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14" s="3">
         <v>46169</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D14" s="27" t="s">
         <v>56</v>
@@ -1420,49 +1415,35 @@
       <c r="E14" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="F14" s="27" t="s">
-        <v>57</v>
+      <c r="F14" s="6" t="s">
+        <v>54</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="H14" s="6" t="s">
         <v>17</v>
       </c>
       <c r="I14" s="12"/>
     </row>
-    <row r="15" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="B15" s="3">
-        <v>46169</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="D15" s="27" t="s">
-        <v>60</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="G15" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="H15" s="6" t="s">
-        <v>17</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B15" s="3"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="6"/>
       <c r="I15" s="12"/>
     </row>
     <row r="16" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B16" s="3"/>
       <c r="C16" s="9"/>
@@ -1476,7 +1457,7 @@
     <row r="17" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="9"/>
@@ -1490,7 +1471,7 @@
     <row r="18" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="9"/>
@@ -1504,7 +1485,7 @@
     <row r="19" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B19" s="3"/>
       <c r="C19" s="9"/>
@@ -1518,7 +1499,7 @@
     <row r="20" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="9"/>
@@ -1532,7 +1513,7 @@
     <row r="21" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="9"/>
@@ -1546,7 +1527,7 @@
     <row r="22" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B22" s="3"/>
       <c r="C22" s="9"/>
@@ -1560,7 +1541,7 @@
     <row r="23" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B23" s="3"/>
       <c r="C23" s="9"/>
@@ -1574,7 +1555,7 @@
     <row r="24" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B24" s="3"/>
       <c r="C24" s="9"/>
@@ -1588,7 +1569,7 @@
     <row r="25" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B25" s="3"/>
       <c r="C25" s="9"/>
@@ -1602,7 +1583,7 @@
     <row r="26" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B26" s="3"/>
       <c r="C26" s="9"/>
@@ -1616,7 +1597,7 @@
     <row r="27" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B27" s="3"/>
       <c r="C27" s="9"/>
@@ -1630,7 +1611,7 @@
     <row r="28" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B28" s="3"/>
       <c r="C28" s="9"/>
@@ -1644,7 +1625,7 @@
     <row r="29" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B29" s="3"/>
       <c r="C29" s="9"/>
@@ -1658,7 +1639,7 @@
     <row r="30" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B30" s="3"/>
       <c r="C30" s="9"/>
@@ -1672,7 +1653,7 @@
     <row r="31" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="9"/>
@@ -1686,7 +1667,7 @@
     <row r="32" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B32" s="3"/>
       <c r="C32" s="9"/>
@@ -1700,7 +1681,7 @@
     <row r="33" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B33" s="3"/>
       <c r="C33" s="9"/>
@@ -1714,7 +1695,7 @@
     <row r="34" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <f t="shared" si="0"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B34" s="3"/>
       <c r="C34" s="9"/>
@@ -1728,7 +1709,7 @@
     <row r="35" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <f t="shared" si="0"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B35" s="3"/>
       <c r="C35" s="9"/>
@@ -1742,7 +1723,7 @@
     <row r="36" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <f t="shared" si="0"/>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B36" s="3"/>
       <c r="C36" s="9"/>
@@ -1756,7 +1737,7 @@
     <row r="37" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <f t="shared" si="0"/>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B37" s="3"/>
       <c r="C37" s="9"/>
@@ -1770,7 +1751,7 @@
     <row r="38" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <f t="shared" si="0"/>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B38" s="3"/>
       <c r="C38" s="9"/>
@@ -1784,7 +1765,7 @@
     <row r="39" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <f t="shared" si="0"/>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B39" s="3"/>
       <c r="C39" s="9"/>
@@ -1798,7 +1779,7 @@
     <row r="40" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <f t="shared" si="0"/>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B40" s="3"/>
       <c r="C40" s="9"/>
@@ -1812,7 +1793,7 @@
     <row r="41" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <f t="shared" si="0"/>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B41" s="3"/>
       <c r="C41" s="9"/>
@@ -1826,7 +1807,7 @@
     <row r="42" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <f t="shared" si="0"/>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B42" s="3"/>
       <c r="C42" s="9"/>
@@ -1840,7 +1821,7 @@
     <row r="43" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <f t="shared" si="0"/>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B43" s="3"/>
       <c r="C43" s="9"/>
@@ -1854,7 +1835,7 @@
     <row r="44" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <f t="shared" si="0"/>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B44" s="3"/>
       <c r="C44" s="9"/>
@@ -1868,7 +1849,7 @@
     <row r="45" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <f t="shared" si="0"/>
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B45" s="3"/>
       <c r="C45" s="9"/>
@@ -1882,7 +1863,7 @@
     <row r="46" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <f t="shared" si="0"/>
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B46" s="3"/>
       <c r="C46" s="9"/>
@@ -1896,7 +1877,7 @@
     <row r="47" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <f t="shared" si="0"/>
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B47" s="3"/>
       <c r="C47" s="9"/>
@@ -1910,7 +1891,7 @@
     <row r="48" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <f t="shared" si="0"/>
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B48" s="3"/>
       <c r="C48" s="9"/>
@@ -1921,33 +1902,19 @@
       <c r="H48" s="6"/>
       <c r="I48" s="12"/>
     </row>
-    <row r="49" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A49" s="1">
-        <f t="shared" si="0"/>
-        <v>47</v>
-      </c>
-      <c r="B49" s="3"/>
-      <c r="C49" s="9"/>
-      <c r="D49" s="6"/>
-      <c r="E49" s="9"/>
-      <c r="F49" s="6"/>
-      <c r="G49" s="9"/>
-      <c r="H49" s="6"/>
-      <c r="I49" s="12"/>
-    </row>
-    <row r="50" spans="1:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="2">
+    <row r="49" spans="1:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="2">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
-      <c r="B50" s="4"/>
-      <c r="C50" s="10"/>
-      <c r="D50" s="7"/>
-      <c r="E50" s="10"/>
-      <c r="F50" s="7"/>
-      <c r="G50" s="10"/>
-      <c r="H50" s="7"/>
-      <c r="I50" s="13"/>
+      <c r="B49" s="4"/>
+      <c r="C49" s="10"/>
+      <c r="D49" s="7"/>
+      <c r="E49" s="10"/>
+      <c r="F49" s="7"/>
+      <c r="G49" s="10"/>
+      <c r="H49" s="7"/>
+      <c r="I49" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1960,7 +1927,7 @@
           <x14:formula1>
             <xm:f>Sheet2!$A$1:$A$2</xm:f>
           </x14:formula1>
-          <xm:sqref>E2:E51</xm:sqref>
+          <xm:sqref>E2:E50</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
